--- a/data/personalia/5 PWT.xlsx
+++ b/data/personalia/5 PWT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07F67547-45CD-4A90-BF9C-578A61DDE309}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD13613-B6F2-41D8-AEED-0B4B1BFEB9E5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2474,6 +2474,9 @@
       <c r="J23" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="K23" s="6">
+        <v>34669</v>
+      </c>
       <c r="L23" s="6">
         <v>25836</v>
       </c>

--- a/data/personalia/5 PWT.xlsx
+++ b/data/personalia/5 PWT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD13613-B6F2-41D8-AEED-0B4B1BFEB9E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95367624-21E1-43F6-9B45-2B1B56369526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="361">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,12 +172,117 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
     <t>Pelaksana Informasi dan Evaluasi</t>
   </si>
   <si>
-    <t>Teknisi</t>
-  </si>
-  <si>
     <t>5 PWT</t>
   </si>
   <si>
@@ -178,12 +292,18 @@
     <t>Manager STL Daop 5 Pwt</t>
   </si>
   <si>
+    <t>PMP.090476.01065</t>
+  </si>
+  <si>
     <t>ARIS FAJAR PURNOMO</t>
   </si>
   <si>
     <t>QC STL 5A Pwt</t>
   </si>
   <si>
+    <t>PMP.010276.00953</t>
+  </si>
+  <si>
     <t>KUS BUDIYONO</t>
   </si>
   <si>
@@ -196,33 +316,51 @@
     <t>QC STL 5C Kta</t>
   </si>
   <si>
+    <t>PMP.180675.128215</t>
+  </si>
+  <si>
     <t>LARAS BHINAR GRAHITA</t>
   </si>
   <si>
     <t>AM Informasi dan Evaluasi Daop 5 Pwt</t>
   </si>
   <si>
+    <t>PRP.250792.39444</t>
+  </si>
+  <si>
     <t>TOMI PEBRIANSA PUTRA</t>
   </si>
   <si>
     <t>AM Kegiatan dan Pembiayaan Daop 5 Pwt</t>
   </si>
   <si>
+    <t>PMP.10021989.32973</t>
+  </si>
+  <si>
     <t>TEDJO RAHARSO</t>
   </si>
   <si>
     <t>AM Perencanaan Teknis Daop 5 Pwt</t>
   </si>
   <si>
+    <t>PMP.021074.41264</t>
+  </si>
+  <si>
     <t>NUR ROCHMAN</t>
   </si>
   <si>
+    <t>PRP.020690.00432</t>
+  </si>
+  <si>
     <t>FENA ROSITA PUTERI</t>
   </si>
   <si>
     <t>Pelaksana Kegiatan dan Pembiayaan</t>
   </si>
   <si>
+    <t>PRP.080593.126884</t>
+  </si>
+  <si>
     <t>HENGGAR BUDIANTO</t>
   </si>
   <si>
@@ -238,30 +376,48 @@
     <t>WS Pwt</t>
   </si>
   <si>
+    <t>PRP.101075.126224</t>
+  </si>
+  <si>
+    <t>PMP.101075.71212</t>
+  </si>
+  <si>
     <t>SARWONO</t>
   </si>
   <si>
     <t>Supervisor Perbaikan UPT Workshop Sintelis Purwokerto</t>
   </si>
   <si>
+    <t>PRP.050488.128661</t>
+  </si>
+  <si>
     <t>AKHMAD MASRURI</t>
   </si>
   <si>
     <t>Supervisor Rekayasa Perawatan UPT Workshop Sintelis Purwokerto</t>
   </si>
   <si>
+    <t>PRP.070380.126227</t>
+  </si>
+  <si>
     <t>EKO HARYONO</t>
   </si>
   <si>
     <t>Teknisi Subunit Perbaikan Workshop</t>
   </si>
   <si>
+    <t>PRP.270288.00288</t>
+  </si>
+  <si>
     <t>AKHMAD MANSUR</t>
   </si>
   <si>
     <t>Teknisi Subunit Perawatan Workshop</t>
   </si>
   <si>
+    <t>PRP.250392.02360</t>
+  </si>
+  <si>
     <t>WAHYU TRI HARYONO</t>
   </si>
   <si>
@@ -271,39 +427,63 @@
     <t>5.1 Ppk</t>
   </si>
   <si>
+    <t>PRP.131083.126482</t>
+  </si>
+  <si>
     <t>EKA SETIA JIMANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.1 Ppk</t>
   </si>
   <si>
+    <t>PRP.050389.00364</t>
+  </si>
+  <si>
     <t>AGUS LASMONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.1 Ppk</t>
   </si>
   <si>
+    <t>PRP.150876.127050</t>
+  </si>
+  <si>
     <t>BAYU ARDIANSYAH</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.1 Ppk</t>
   </si>
   <si>
+    <t>PRP.181289.00391</t>
+  </si>
+  <si>
     <t>AKHDAN DZAKY WIJATOMO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.1 Ppk</t>
   </si>
   <si>
+    <t>PRP.250702.67884</t>
+  </si>
+  <si>
     <t>MISBAHUL MUNIR</t>
   </si>
   <si>
+    <t>PRP.250791.00435</t>
+  </si>
+  <si>
     <t>SOBIRIN</t>
   </si>
   <si>
+    <t>PRP.250970.00466</t>
+  </si>
+  <si>
     <t>SUTRISNO</t>
   </si>
   <si>
+    <t>PRP.120971.00472</t>
+  </si>
+  <si>
     <t>FIDIAR FAUZI</t>
   </si>
   <si>
@@ -313,39 +493,66 @@
     <t>5.2 Krr</t>
   </si>
   <si>
+    <t>PRP.120187.126226</t>
+  </si>
+  <si>
+    <t>PMP.120187.71213</t>
+  </si>
+  <si>
     <t>JUMERI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.2 Krr</t>
   </si>
   <si>
+    <t>PRP.020181.00323</t>
+  </si>
+  <si>
     <t>TYARSAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.2 Krr</t>
   </si>
   <si>
+    <t>PRP.040972.126752</t>
+  </si>
+  <si>
     <t>ART CHRISTY JUNERITA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.2 Krr</t>
   </si>
   <si>
+    <t>PRP.020189.00356</t>
+  </si>
+  <si>
     <t>AGUS PRIANTO</t>
   </si>
   <si>
+    <t>PRP.100894.02350</t>
+  </si>
+  <si>
     <t>ZULFIKRI NUR FAIZ</t>
   </si>
   <si>
+    <t>PRP.030702.72278</t>
+  </si>
+  <si>
     <t>IMAM SUTOPO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.2 Krr</t>
   </si>
   <si>
+    <t>PRP.211071.00359</t>
+  </si>
+  <si>
     <t>AKHMAD BASITH JAFAD</t>
   </si>
   <si>
+    <t>PRP.230291.00321</t>
+  </si>
+  <si>
     <t>TITO ANTONY</t>
   </si>
   <si>
@@ -355,42 +562,72 @@
     <t>5.3 Pwt</t>
   </si>
   <si>
+    <t>PRP.040974.00468</t>
+  </si>
+  <si>
+    <t>PMP.040974.66914</t>
+  </si>
+  <si>
     <t>HERI SUSANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 5.3 Pwt</t>
   </si>
   <si>
+    <t>PRP.040190.126220</t>
+  </si>
+  <si>
     <t>GONDO SUDARMANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 5.3 Pwt</t>
   </si>
   <si>
+    <t>PRP.051276.126634</t>
+  </si>
+  <si>
     <t>DANANG MA'RUF</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.3 Pwt</t>
   </si>
   <si>
+    <t>PRP.210598.71441</t>
+  </si>
+  <si>
     <t>ADI NUR ALAMSYAH</t>
   </si>
   <si>
+    <t>PRP.131191.00258</t>
+  </si>
+  <si>
     <t>JODI KRISTIAN SIMANULLANG</t>
   </si>
   <si>
+    <t>PRP.271199.45593</t>
+  </si>
+  <si>
     <t>ALFIAN KOSJIANTO PUTRA</t>
   </si>
   <si>
+    <t>PRP.051001.67303</t>
+  </si>
+  <si>
     <t>ELFANDA FARHANTIA SURY</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.3 Pwt</t>
   </si>
   <si>
+    <t>PRP.160102.58626</t>
+  </si>
+  <si>
     <t>ESHA ADI NUGRAHA</t>
   </si>
   <si>
+    <t>PRP.161286.00261</t>
+  </si>
+  <si>
     <t>IMAN TEGUH SANTOSO</t>
   </si>
   <si>
@@ -400,12 +637,18 @@
     <t>5.4 Sdr</t>
   </si>
   <si>
+    <t>PRP.090873.126879</t>
+  </si>
+  <si>
     <t>RETFAEDI ARIFIBOWO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.4 Sdr</t>
   </si>
   <si>
+    <t>PRP.230388.00284</t>
+  </si>
+  <si>
     <t>AZIS SAPUTRA</t>
   </si>
   <si>
@@ -418,21 +661,36 @@
     <t>PNC Perbaikan UPT Resor STL 5.4 Sdr</t>
   </si>
   <si>
+    <t>PRP.170701.71331</t>
+  </si>
+  <si>
     <t>M ALLIFONNI RIZALDY</t>
   </si>
   <si>
+    <t>PRP.220796.38549</t>
+  </si>
+  <si>
     <t>M FACH RIZAL JAM ANI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.4 Sdr</t>
   </si>
   <si>
+    <t>PRP.250403.57199</t>
+  </si>
+  <si>
     <t>DEA AGUNG EKA SAPUTRA</t>
   </si>
   <si>
+    <t>PRP.220995.02355</t>
+  </si>
+  <si>
     <t>RIYAN VENTIANTO</t>
   </si>
   <si>
+    <t>PRP.070886.00514</t>
+  </si>
+  <si>
     <t>ANDI BUDI MAWAN</t>
   </si>
   <si>
@@ -442,42 +700,72 @@
     <t>5.5 Kwg</t>
   </si>
   <si>
+    <t>PRP.060876.126638</t>
+  </si>
+  <si>
+    <t>PMP.060876.71211</t>
+  </si>
+  <si>
     <t>YUGO NUGROHO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.5 Kwg</t>
   </si>
   <si>
+    <t>PRP.280481.00430</t>
+  </si>
+  <si>
     <t>M ALDO RAVY ALBAR</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.5 Kwg</t>
   </si>
   <si>
+    <t>PRP.120589.00464</t>
+  </si>
+  <si>
     <t>MUHAMMAD WILDAN NISFA SABANI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.5 Kwg</t>
   </si>
   <si>
+    <t>PRP.27011994.37012</t>
+  </si>
+  <si>
     <t>PRIANGKOSO BUDI</t>
   </si>
   <si>
+    <t>PRP.140692.41403</t>
+  </si>
+  <si>
     <t>BAGUS SETYO WIBOWO</t>
   </si>
   <si>
+    <t>PRP.200301.63938</t>
+  </si>
+  <si>
     <t>SUPARYONO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.5 Kwg</t>
   </si>
   <si>
+    <t>PRP.051281.00428</t>
+  </si>
+  <si>
     <t>SINAR YUDHA SIMAN TOMO</t>
   </si>
   <si>
+    <t>PRP.160994.38874</t>
+  </si>
+  <si>
     <t>IMAM NUR HUDA</t>
   </si>
   <si>
+    <t>PRP.060304.72276</t>
+  </si>
+  <si>
     <t>MUHAMAD ZAELANI</t>
   </si>
   <si>
@@ -487,45 +775,75 @@
     <t>5.6 Ma</t>
   </si>
   <si>
+    <t>PRP.021187.128060</t>
+  </si>
+  <si>
     <t>RAHMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.6 Ma</t>
   </si>
   <si>
+    <t>PRP.220976.126880</t>
+  </si>
+  <si>
     <t>AGIN HANDOKO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.6 Ma</t>
   </si>
   <si>
+    <t>PRP.030586.00353</t>
+  </si>
+  <si>
     <t>KEN ARYA SYAH PUTRA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.6 Ma</t>
   </si>
   <si>
+    <t>PRP.031202.64778</t>
+  </si>
+  <si>
     <t>LUCKY ISA MUKTI</t>
   </si>
   <si>
+    <t>PRP.220699.76814</t>
+  </si>
+  <si>
     <t>RIYAN DENY ADIUNUS</t>
   </si>
   <si>
+    <t>PRP.070794.02357</t>
+  </si>
+  <si>
     <t>APHIT SANDY TAURUSELA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.6 Ma</t>
   </si>
   <si>
+    <t>PRP.270493.02352</t>
+  </si>
+  <si>
     <t>WAHYU ADI INDRA GUNAWAN</t>
   </si>
   <si>
+    <t>PRP.090691.02351</t>
+  </si>
+  <si>
     <t>LUKI ANDRIYAN</t>
   </si>
   <si>
+    <t>PRP.210893.02353</t>
+  </si>
+  <si>
     <t>GERY ARYANDA</t>
   </si>
   <si>
+    <t>PRP.141002.65228</t>
+  </si>
+  <si>
     <t>AJI SARWONO</t>
   </si>
   <si>
@@ -535,42 +853,69 @@
     <t>5.7 Kya</t>
   </si>
   <si>
+    <t>PMP.291179.69812</t>
+  </si>
+  <si>
     <t>PUJI HARSONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.7 Kya</t>
   </si>
   <si>
+    <t>PRP.120774.126878</t>
+  </si>
+  <si>
     <t>ARI TRI NURCAHYONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.7 Kya</t>
   </si>
   <si>
+    <t>PRP.150176.128458</t>
+  </si>
+  <si>
     <t>DWI PUTRA MANTIAS MUZNI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.7 Kya</t>
   </si>
   <si>
+    <t>PRP.200590.00260</t>
+  </si>
+  <si>
     <t>NUR TAUFIK SETYAWAN</t>
   </si>
   <si>
+    <t>PRP.181189.00434</t>
+  </si>
+  <si>
     <t>ANGGIT YUDHA BAGASKARA</t>
   </si>
   <si>
+    <t>PRP.230398.67728</t>
+  </si>
+  <si>
     <t>IWAN SETIA NUR ILLAHI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.7 Kya</t>
   </si>
   <si>
+    <t>PRP.111186.00290</t>
+  </si>
+  <si>
     <t>SUDIYONO</t>
   </si>
   <si>
+    <t>PRP.240788.00509</t>
+  </si>
+  <si>
     <t>RIZKI NOVRIYADI</t>
   </si>
   <si>
+    <t>PRP.011196.02354</t>
+  </si>
+  <si>
     <t>SUPARTO</t>
   </si>
   <si>
@@ -580,27 +925,45 @@
     <t>5.8 Gb</t>
   </si>
   <si>
+    <t>PRP.260571.126830</t>
+  </si>
+  <si>
+    <t>PMP.260571.66913</t>
+  </si>
+  <si>
     <t>MOKHAMAD SURIPTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.8 Gb</t>
   </si>
   <si>
+    <t>PRP.080772.126331</t>
+  </si>
+  <si>
     <t>NUR IMAM VATONI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.8 Gb</t>
   </si>
   <si>
+    <t>PRP.121187.00474</t>
+  </si>
+  <si>
     <t>AGUS MULYANTORO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.8 Gb</t>
   </si>
   <si>
+    <t>PRP.070988.00259</t>
+  </si>
+  <si>
     <t>PUNGKY WIDJANARKO</t>
   </si>
   <si>
+    <t>PRP.14011996.37014</t>
+  </si>
+  <si>
     <t>BAHAR BUDI PRATAMA</t>
   </si>
   <si>
@@ -610,9 +973,15 @@
     <t>PNC Preventif UPT Resor STL 5.8 Gb</t>
   </si>
   <si>
+    <t>PRP.111202.65637</t>
+  </si>
+  <si>
     <t>MIFTAKUL NUR ARIFIN</t>
   </si>
   <si>
+    <t>PRP.18121995.37376</t>
+  </si>
+  <si>
     <t>DAIMAN</t>
   </si>
   <si>
@@ -622,39 +991,63 @@
     <t>5.9 Km</t>
   </si>
   <si>
+    <t>PRP.050383.126633</t>
+  </si>
+  <si>
     <t>AMIN MAKHFUD</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 5.9 Km</t>
   </si>
   <si>
+    <t>PRP.270280.126481</t>
+  </si>
+  <si>
     <t>FERI ARFIAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 5.9 Km</t>
   </si>
   <si>
+    <t>PRP.110189.122756</t>
+  </si>
+  <si>
     <t>SUDIR</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.9 Km</t>
   </si>
   <si>
+    <t>PRP.091171.00469</t>
+  </si>
+  <si>
     <t>LUKMAN NUL HAKIM</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.9 Km</t>
   </si>
   <si>
+    <t>PRP.290798.72014</t>
+  </si>
+  <si>
     <t>ILHAM NUR KHOLID</t>
   </si>
   <si>
+    <t>PRP.060203.64777</t>
+  </si>
+  <si>
     <t>AMIN SUPRIYONO</t>
   </si>
   <si>
+    <t>PRP.29051978.38032</t>
+  </si>
+  <si>
     <t>WAHYUDI BANU HARTOYO</t>
   </si>
   <si>
+    <t>PRP.23011976.33809</t>
+  </si>
+  <si>
     <t>RAHMAT AHMADI</t>
   </si>
   <si>
@@ -664,6 +1057,9 @@
     <t>1.9 Mri</t>
   </si>
   <si>
+    <t>PRP.250677.126086</t>
+  </si>
+  <si>
     <t>SIGIT EKO PRASETYA</t>
   </si>
   <si>
@@ -673,289 +1069,58 @@
     <t>5.10 Kta</t>
   </si>
   <si>
+    <t>PRP.310172.02165</t>
+  </si>
+  <si>
     <t>RAJIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 5.10 Kta</t>
   </si>
   <si>
+    <t>PRP.080875.126223</t>
+  </si>
+  <si>
     <t>PARYANTO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 5.10 Kta</t>
   </si>
   <si>
+    <t>PRP.060786.00473</t>
+  </si>
+  <si>
     <t>AGUS SUMARNO</t>
   </si>
   <si>
+    <t>PRP.230887.00320</t>
+  </si>
+  <si>
     <t>NANANG SISWANTO</t>
   </si>
   <si>
+    <t>PRP.130971.00465</t>
+  </si>
+  <si>
     <t>AMIRULLAH AFI ADANI</t>
   </si>
   <si>
+    <t>PRP.240204.67601</t>
+  </si>
+  <si>
     <t>SUNGKONO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 5.10 Kta</t>
   </si>
   <si>
+    <t>PRP.270472.00467</t>
+  </si>
+  <si>
     <t>FAJAR DWI PERMANA</t>
   </si>
   <si>
-    <t>PMP.090476.01065</t>
-  </si>
-  <si>
-    <t>PMP. 010276. 00953</t>
-  </si>
-  <si>
-    <t>PRP. 130974. 126881</t>
-  </si>
-  <si>
-    <t>PMP. 180675. 128215</t>
-  </si>
-  <si>
-    <t>PRP.250792.39444</t>
-  </si>
-  <si>
-    <t>PMP.10021989.32973</t>
-  </si>
-  <si>
-    <t>PMP.021074.41264</t>
-  </si>
-  <si>
-    <t>PRP.020690.00432</t>
-  </si>
-  <si>
-    <t>PRP.080593.126884</t>
-  </si>
-  <si>
-    <t>PRP.050488.128661</t>
-  </si>
-  <si>
-    <t>PRP.070380.126227</t>
-  </si>
-  <si>
-    <t>PRP.270288.00288</t>
-  </si>
-  <si>
-    <t>PRP.250392.02360</t>
-  </si>
-  <si>
-    <t>PRP.131083.126482</t>
-  </si>
-  <si>
-    <t>PRP.150876.127050</t>
-  </si>
-  <si>
-    <t>PRP.181289.00391</t>
-  </si>
-  <si>
-    <t>PRP.250702.67884</t>
-  </si>
-  <si>
-    <t>PRP.250791.00435</t>
-  </si>
-  <si>
-    <t>PRP.250970.00466</t>
-  </si>
-  <si>
-    <t>PRP.120971.00472</t>
-  </si>
-  <si>
-    <t>PRP.020181.00323</t>
-  </si>
-  <si>
-    <t>PRP.040972.126752</t>
-  </si>
-  <si>
-    <t>PRP.020189.00356</t>
-  </si>
-  <si>
-    <t>PRP.030702.72278</t>
-  </si>
-  <si>
-    <t>PRP.211071.00359</t>
-  </si>
-  <si>
-    <t>PRP.230291.00321</t>
-  </si>
-  <si>
-    <t>PRP.040974.00468</t>
-  </si>
-  <si>
-    <t>PRP.040190.126220</t>
-  </si>
-  <si>
-    <t>PRP.210598.71441</t>
-  </si>
-  <si>
-    <t>PRP.131191.00258</t>
-  </si>
-  <si>
-    <t>PRP.271199.45593</t>
-  </si>
-  <si>
-    <t>PRP.051001.67303</t>
-  </si>
-  <si>
-    <t>PRP.160102.58626</t>
-  </si>
-  <si>
-    <t>PRP.161286.00261</t>
-  </si>
-  <si>
-    <t>PRP.090873.126879</t>
-  </si>
-  <si>
-    <t>PRP. 090688. 00286</t>
-  </si>
-  <si>
-    <t>PRP.170701.71331</t>
-  </si>
-  <si>
-    <t>PRP.250403.57199</t>
-  </si>
-  <si>
-    <t>PRP.070886.00514</t>
-  </si>
-  <si>
-    <t>PRP.060876.126638</t>
-  </si>
-  <si>
-    <t>PRP.120589.00464</t>
-  </si>
-  <si>
-    <t>PRP.27011994.37012</t>
-  </si>
-  <si>
-    <t>PRP.140692.41403</t>
-  </si>
-  <si>
-    <t>PRP.200301.63938</t>
-  </si>
-  <si>
-    <t>PRP.051281.00428</t>
-  </si>
-  <si>
-    <t>PRP.160994.38874</t>
-  </si>
-  <si>
-    <t>PRP.060304.72276</t>
-  </si>
-  <si>
-    <t>PRP.021187.128060</t>
-  </si>
-  <si>
-    <t>PRP.030586.00353</t>
-  </si>
-  <si>
-    <t>PRP.031202.64778</t>
-  </si>
-  <si>
-    <t>PRP.220699.76814</t>
-  </si>
-  <si>
-    <t>PRP.070794.02357</t>
-  </si>
-  <si>
-    <t>PRP.090691.02351</t>
-  </si>
-  <si>
-    <t>PRP.210893.02353</t>
-  </si>
-  <si>
-    <t>PRP.141002.65228</t>
-  </si>
-  <si>
-    <t>PRP.291179.128065</t>
-  </si>
-  <si>
-    <t>PRP.150176.128458</t>
-  </si>
-  <si>
-    <t>PRP.181189.00434</t>
-  </si>
-  <si>
-    <t>PRP.111186.00290</t>
-  </si>
-  <si>
-    <t>PRP.240788.00509</t>
-  </si>
-  <si>
-    <t>PRP.011196.02354</t>
-  </si>
-  <si>
-    <t>PRP.080772.126331</t>
-  </si>
-  <si>
-    <t>PRP.121187.00474</t>
-  </si>
-  <si>
-    <t>PRP.070988.00259</t>
-  </si>
-  <si>
-    <t>PRP.14011996.37014</t>
-  </si>
-  <si>
-    <t>PRP.111202.65637</t>
-  </si>
-  <si>
-    <t>PRP.050383.126633</t>
-  </si>
-  <si>
-    <t>PRP.270280.126481</t>
-  </si>
-  <si>
-    <t>PRP.110189.122756</t>
-  </si>
-  <si>
-    <t>PRP.091171.00469</t>
-  </si>
-  <si>
-    <t>PRP.290798.72014</t>
-  </si>
-  <si>
-    <t>PRP.060203.64777</t>
-  </si>
-  <si>
-    <t>PRP.29051978.38032</t>
-  </si>
-  <si>
-    <t>PRP.080875.126223</t>
-  </si>
-  <si>
-    <t>PRP.060786.00473</t>
-  </si>
-  <si>
-    <t>PRP.230887.00320</t>
-  </si>
-  <si>
-    <t>PRP.130971.00465</t>
-  </si>
-  <si>
-    <t>PRP.240204.67601</t>
-  </si>
-  <si>
-    <t>PRP.270472.00467</t>
-  </si>
-  <si>
     <t>PRP.230591.02314</t>
-  </si>
-  <si>
-    <t>PMP.010276.00953</t>
-  </si>
-  <si>
-    <t>PMP.180675.128215</t>
-  </si>
-  <si>
-    <t>PMP.040974.66914</t>
-  </si>
-  <si>
-    <t>PMP.060876.71211</t>
-  </si>
-  <si>
-    <t>PMP.291179.69812</t>
   </si>
 </sst>
 </file>
@@ -1026,9 +1191,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1037,8 +1199,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1342,30 +1507,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T102"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1551,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1396,19 +1560,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1417,7 +1581,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1429,10 +1593,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>45690</v>
@@ -1443,13 +1607,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>48</v>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45901</v>
       </c>
       <c r="I2" s="2">
@@ -1458,35 +1622,31 @@
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>35490</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>27859</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>48335</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="6">
-        <v>45740</v>
-      </c>
       <c r="Q2" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="R2" s="6">
+        <v>84</v>
+      </c>
+      <c r="R2" s="5">
         <v>47324</v>
       </c>
-      <c r="S2" s="3"/>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2">
         <v>44430</v>
@@ -1497,13 +1657,13 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>50</v>
+      <c r="F3" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45884</v>
       </c>
       <c r="I3" s="2">
@@ -1512,35 +1672,31 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>35217</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>27791</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>48274</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O3" s="6">
-        <v>45696</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="R3" s="6">
+        <v>87</v>
+      </c>
+      <c r="R3" s="5">
         <v>47265</v>
       </c>
-      <c r="S3" s="3"/>
+      <c r="S3" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2">
         <v>46255</v>
@@ -1551,13 +1707,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>52</v>
+      <c r="F4" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45992</v>
       </c>
       <c r="I4" s="2">
@@ -1566,28 +1722,22 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35490</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>27285</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>47757</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45696</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2">
         <v>41977</v>
@@ -1598,13 +1748,13 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>54</v>
+      <c r="F5" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45884</v>
       </c>
       <c r="I5" s="2">
@@ -1613,35 +1763,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>34669</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>27563</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>48030</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45747</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="R5" s="6">
+        <v>92</v>
+      </c>
+      <c r="R5" s="5">
         <v>47285</v>
       </c>
-      <c r="S5" s="3"/>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2">
         <v>69622</v>
@@ -1652,13 +1798,13 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
+      <c r="F6" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>45962</v>
       </c>
       <c r="I6" s="2">
@@ -1667,29 +1813,31 @@
       <c r="J6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>42562</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>33810</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>54271</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="O6" s="5">
         <v>46446</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="P6" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2">
         <v>62921</v>
@@ -1700,13 +1848,13 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
+      <c r="F7" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>45809</v>
       </c>
       <c r="I7" s="2">
@@ -1715,34 +1863,31 @@
       <c r="J7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>41456</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>32549</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>53022</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="O7" s="6">
+      <c r="Q7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7" s="5">
         <v>46007</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="R7" s="6">
-        <v>46007</v>
+      <c r="S7" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2">
         <v>45748</v>
@@ -1753,14 +1898,14 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
-        <v>44927</v>
+      <c r="H8" s="5">
+        <v>45505</v>
       </c>
       <c r="I8" s="2">
         <v>9</v>
@@ -1768,35 +1913,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
-        <v>35499</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="K8" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L8" s="5">
         <v>27304</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>47788</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8" s="5">
         <v>46448</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="R8" s="6">
-        <v>46448</v>
-      </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>53312</v>
@@ -1807,14 +1948,14 @@
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
+      <c r="F9" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+      <c r="H9" s="5">
+        <v>42110</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -1822,29 +1963,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>39815</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>33026</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>53509</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O9" s="6">
+        <v>103</v>
+      </c>
+      <c r="O9" s="5">
         <v>46006</v>
       </c>
-      <c r="S9" s="3"/>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2">
         <v>62511</v>
@@ -1855,14 +1998,14 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
+      <c r="F10" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+      <c r="H10" s="5">
+        <v>43817</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
@@ -1870,29 +2013,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>41153</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>34097</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>54575</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O10" s="6">
+        <v>106</v>
+      </c>
+      <c r="O10" s="5">
         <v>47203</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2">
         <v>51281</v>
@@ -1903,13 +2048,13 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>65</v>
+      <c r="F11" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>45474</v>
       </c>
       <c r="I11" s="2">
@@ -1918,23 +2063,22 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>39600</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>29271</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>49735</v>
       </c>
-      <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
         <v>46276</v>
@@ -1945,13 +2089,13 @@
       <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>67</v>
+      <c r="F12" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="6">
+        <v>111</v>
+      </c>
+      <c r="H12" s="5">
         <v>45901</v>
       </c>
       <c r="I12" s="2">
@@ -1960,23 +2104,40 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>35490</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>27677</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>48153</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="N12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" s="5">
+        <v>46953</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R12" s="5">
+        <v>47265</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2">
         <v>53211</v>
@@ -1987,13 +2148,13 @@
       <c r="E13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>70</v>
+      <c r="F13" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="6">
+        <v>111</v>
+      </c>
+      <c r="H13" s="5">
         <v>45823</v>
       </c>
       <c r="I13" s="2">
@@ -2002,29 +2163,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>39815</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>32238</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>52718</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="O13" s="6">
+        <v>116</v>
+      </c>
+      <c r="O13" s="5">
         <v>47110</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2">
         <v>49017</v>
@@ -2035,14 +2198,14 @@
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>72</v>
+      <c r="F14" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44927</v>
+        <v>111</v>
+      </c>
+      <c r="H14" s="5">
+        <v>43005</v>
       </c>
       <c r="I14" s="2">
         <v>8</v>
@@ -2050,29 +2213,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>38899</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>29287</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>49766</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="O14" s="6">
+        <v>119</v>
+      </c>
+      <c r="O14" s="5">
         <v>46837</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="P14" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="C15" s="2">
         <v>53209</v>
@@ -2081,16 +2246,16 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="6">
-        <v>45474</v>
+        <v>111</v>
+      </c>
+      <c r="H15" s="5">
+        <v>42501</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
@@ -2098,28 +2263,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>39815</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>32200</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>52657</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O15" s="6">
+        <v>122</v>
+      </c>
+      <c r="O15" s="5">
         <v>46861</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2">
         <v>69450</v>
@@ -2128,16 +2296,16 @@
         <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>76</v>
+        <v>46</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="6">
-        <v>45474</v>
+        <v>111</v>
+      </c>
+      <c r="H16" s="5">
+        <v>44986</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
@@ -2145,29 +2313,31 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>42562</v>
       </c>
-      <c r="L16" s="6">
-        <v>34053</v>
-      </c>
-      <c r="M16" s="6">
-        <v>54514</v>
+      <c r="L16" s="5">
+        <v>33688</v>
+      </c>
+      <c r="M16" s="5">
+        <v>54149</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O16" s="6">
+        <v>125</v>
+      </c>
+      <c r="O16" s="5">
         <v>46208</v>
       </c>
-      <c r="S16" s="3"/>
+      <c r="P16" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C17" s="2">
         <v>49091</v>
@@ -2178,13 +2348,13 @@
       <c r="E17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>78</v>
+      <c r="F17" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="6">
+        <v>128</v>
+      </c>
+      <c r="H17" s="5">
         <v>45672</v>
       </c>
       <c r="I17" s="2">
@@ -2193,29 +2363,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>38899</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>30602</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>51075</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="O17" s="6">
+        <v>129</v>
+      </c>
+      <c r="O17" s="5">
         <v>46861</v>
       </c>
-      <c r="S17" s="3"/>
+      <c r="P17" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C18" s="2">
         <v>53242</v>
@@ -2226,13 +2398,13 @@
       <c r="E18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>81</v>
+      <c r="F18" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="6">
+        <v>128</v>
+      </c>
+      <c r="H18" s="5">
         <v>45915</v>
       </c>
       <c r="I18" s="2">
@@ -2241,23 +2413,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>39815</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>32572</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>53053</v>
       </c>
-      <c r="S18" s="3"/>
+      <c r="N18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="O18" s="5">
+        <v>46937</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2">
         <v>46296</v>
@@ -2268,13 +2448,13 @@
       <c r="E19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>83</v>
+      <c r="F19" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="6">
+        <v>128</v>
+      </c>
+      <c r="H19" s="5">
         <v>45308</v>
       </c>
       <c r="I19" s="2">
@@ -2283,29 +2463,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>35490</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>27987</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>48458</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O19" s="6">
+        <v>135</v>
+      </c>
+      <c r="O19" s="5">
         <v>47110</v>
       </c>
-      <c r="S19" s="3"/>
+      <c r="P19" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2">
         <v>55588</v>
@@ -2316,14 +2498,14 @@
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>85</v>
+      <c r="F20" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="6">
-        <v>44927</v>
+        <v>128</v>
+      </c>
+      <c r="H20" s="5">
+        <v>42019</v>
       </c>
       <c r="I20" s="2">
         <v>5</v>
@@ -2331,29 +2513,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>40163</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>32860</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>53328</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O20" s="6">
+        <v>138</v>
+      </c>
+      <c r="O20" s="5">
         <v>47110</v>
       </c>
-      <c r="S20" s="3"/>
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2">
         <v>75328</v>
@@ -2364,13 +2548,13 @@
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>87</v>
+      <c r="F21" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="6">
+        <v>128</v>
+      </c>
+      <c r="H21" s="5">
         <v>45580</v>
       </c>
       <c r="I21" s="2">
@@ -2379,29 +2563,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>44958</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>37462</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>57923</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="O21" s="6">
+        <v>141</v>
+      </c>
+      <c r="O21" s="5">
         <v>47110</v>
       </c>
-      <c r="S21" s="3"/>
+      <c r="P21" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2">
         <v>55693</v>
@@ -2412,14 +2598,14 @@
       <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>87</v>
+      <c r="F22" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="6">
-        <v>44927</v>
+        <v>128</v>
+      </c>
+      <c r="H22" s="5">
+        <v>44162</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
@@ -2427,28 +2613,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>40163</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>33443</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>53905</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O22" s="6">
+        <v>143</v>
+      </c>
+      <c r="O22" s="5">
         <v>46937</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2">
         <v>42582</v>
@@ -2459,14 +2648,14 @@
       <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>87</v>
+      <c r="F23" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="6">
-        <v>44927</v>
+        <v>128</v>
+      </c>
+      <c r="H23" s="5">
+        <v>42019</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -2474,29 +2663,31 @@
       <c r="J23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>34669</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>25836</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>46296</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O23" s="6">
+        <v>145</v>
+      </c>
+      <c r="O23" s="5">
         <v>47110</v>
       </c>
-      <c r="S23" s="3"/>
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="C24" s="2">
         <v>59227</v>
@@ -2507,14 +2698,14 @@
       <c r="E24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>87</v>
+      <c r="F24" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="6">
-        <v>44927</v>
+        <v>128</v>
+      </c>
+      <c r="H24" s="5">
+        <v>44531</v>
       </c>
       <c r="I24" s="2">
         <v>5</v>
@@ -2522,29 +2713,31 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>40575</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>26188</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>46661</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O24" s="6">
+        <v>147</v>
+      </c>
+      <c r="O24" s="5">
         <v>47110</v>
       </c>
-      <c r="S24" s="3"/>
+      <c r="P24" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="C25" s="2">
         <v>49936</v>
@@ -2555,13 +2748,13 @@
       <c r="E25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>92</v>
+      <c r="F25" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="6">
+        <v>150</v>
+      </c>
+      <c r="H25" s="5">
         <v>45915</v>
       </c>
       <c r="I25" s="2">
@@ -2570,23 +2763,40 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>39387</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>31789</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>52263</v>
       </c>
-      <c r="S25" s="3"/>
+      <c r="N25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="O25" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="R25" s="5">
+        <v>47265</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2">
         <v>49054</v>
@@ -2597,13 +2807,13 @@
       <c r="E26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>95</v>
+      <c r="F26" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="6">
+        <v>150</v>
+      </c>
+      <c r="H26" s="5">
         <v>45308</v>
       </c>
       <c r="I26" s="2">
@@ -2612,29 +2822,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L26" s="6">
-        <v>29618</v>
-      </c>
-      <c r="M26" s="6">
-        <v>50100</v>
+      <c r="K26" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L26" s="5">
+        <v>29588</v>
+      </c>
+      <c r="M26" s="5">
+        <v>50072</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O26" s="6">
+        <v>155</v>
+      </c>
+      <c r="O26" s="5">
         <v>46697</v>
       </c>
-      <c r="S26" s="3"/>
+      <c r="P26" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="27" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2">
         <v>46224</v>
@@ -2645,13 +2857,13 @@
       <c r="E27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>97</v>
+      <c r="F27" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="6">
+        <v>150</v>
+      </c>
+      <c r="H27" s="5">
         <v>45566</v>
       </c>
       <c r="I27" s="2">
@@ -2660,29 +2872,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>35490</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>26546</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>47027</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O27" s="6">
+        <v>158</v>
+      </c>
+      <c r="O27" s="5">
         <v>47110</v>
       </c>
-      <c r="S27" s="3"/>
+      <c r="P27" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2">
         <v>53232</v>
@@ -2693,14 +2907,14 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>99</v>
+      <c r="F28" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="6">
-        <v>44927</v>
+        <v>150</v>
+      </c>
+      <c r="H28" s="5">
+        <v>44531</v>
       </c>
       <c r="I28" s="2">
         <v>5</v>
@@ -2708,29 +2922,31 @@
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>39815</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>32510</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>52994</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="O28" s="6">
+        <v>161</v>
+      </c>
+      <c r="O28" s="5">
         <v>46837</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="C29" s="2">
         <v>69939</v>
@@ -2741,13 +2957,13 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>99</v>
+      <c r="F29" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H29" s="6">
+        <v>150</v>
+      </c>
+      <c r="H29" s="5">
         <v>45597</v>
       </c>
       <c r="I29" s="2">
@@ -2756,23 +2972,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>42597</v>
       </c>
-      <c r="L29" s="6">
-        <v>34615</v>
-      </c>
-      <c r="M29" s="6">
-        <v>55093</v>
-      </c>
-      <c r="S29" s="3"/>
+      <c r="L29" s="5">
+        <v>34556</v>
+      </c>
+      <c r="M29" s="5">
+        <v>55032</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O29" s="5">
+        <v>46120</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="C30" s="2">
         <v>75341</v>
@@ -2783,13 +3007,13 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>99</v>
+      <c r="F30" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" s="6">
+        <v>150</v>
+      </c>
+      <c r="H30" s="5">
         <v>45853</v>
       </c>
       <c r="I30" s="2">
@@ -2798,28 +3022,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
-        <v>44927</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="K30" s="5">
+        <v>44958</v>
+      </c>
+      <c r="L30" s="5">
         <v>37440</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>57923</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O30" s="6">
+        <v>165</v>
+      </c>
+      <c r="O30" s="5">
         <v>47285</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2">
         <v>51194</v>
@@ -2830,13 +3057,13 @@
       <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>103</v>
+      <c r="F31" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="6">
+        <v>150</v>
+      </c>
+      <c r="H31" s="5">
         <v>45383</v>
       </c>
       <c r="I31" s="2">
@@ -2845,29 +3072,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>39600</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="5">
         <v>26227</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="5">
         <v>46692</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="O31" s="6">
+        <v>168</v>
+      </c>
+      <c r="O31" s="5">
         <v>47110</v>
       </c>
-      <c r="S31" s="3"/>
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="C32" s="2">
         <v>55576</v>
@@ -2878,14 +3107,14 @@
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>103</v>
+      <c r="F32" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H32" s="6">
-        <v>44927</v>
+        <v>150</v>
+      </c>
+      <c r="H32" s="5">
+        <v>44531</v>
       </c>
       <c r="I32" s="2">
         <v>5</v>
@@ -2893,29 +3122,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>40163</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>33292</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>53752</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O32" s="6">
+        <v>170</v>
+      </c>
+      <c r="O32" s="5">
         <v>47110</v>
       </c>
-      <c r="S32" s="3"/>
+      <c r="P32" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="C33" s="2">
         <v>46254</v>
@@ -2926,13 +3157,13 @@
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>106</v>
+      <c r="F33" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" s="6">
+        <v>173</v>
+      </c>
+      <c r="H33" s="5">
         <v>45901</v>
       </c>
       <c r="I33" s="2">
@@ -2941,35 +3172,40 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>35490</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>27276</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>47757</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O33" s="6">
+        <v>174</v>
+      </c>
+      <c r="O33" s="5">
         <v>46819</v>
       </c>
+      <c r="P33" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q33" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="R33" s="6">
+        <v>175</v>
+      </c>
+      <c r="R33" s="5">
         <v>47097</v>
       </c>
-      <c r="S33" s="3"/>
+      <c r="S33" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2">
         <v>54404</v>
@@ -2980,13 +3216,13 @@
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>109</v>
+      <c r="F34" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H34" s="6">
+        <v>173</v>
+      </c>
+      <c r="H34" s="5">
         <v>45915</v>
       </c>
       <c r="I34" s="2">
@@ -2995,29 +3231,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L34" s="6">
-        <v>32964</v>
-      </c>
-      <c r="M34" s="6">
-        <v>53448</v>
+      <c r="K34" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L34" s="5">
+        <v>32877</v>
+      </c>
+      <c r="M34" s="5">
+        <v>53359</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O34" s="6">
+        <v>178</v>
+      </c>
+      <c r="O34" s="5">
         <v>46851</v>
       </c>
-      <c r="S34" s="3"/>
+      <c r="P34" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="35" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C35" s="2">
         <v>44440</v>
@@ -3028,13 +3266,13 @@
       <c r="E35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>111</v>
+      <c r="F35" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35" s="6">
+        <v>173</v>
+      </c>
+      <c r="H35" s="5">
         <v>45308</v>
       </c>
       <c r="I35" s="2">
@@ -3043,23 +3281,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L35" s="6">
-        <v>27892</v>
-      </c>
-      <c r="M35" s="6">
-        <v>48366</v>
-      </c>
-      <c r="S35" s="3"/>
+      <c r="K35" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L35" s="5">
+        <v>28099</v>
+      </c>
+      <c r="M35" s="5">
+        <v>48580</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="O35" s="5">
+        <v>47110</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="C36" s="2">
         <v>74610</v>
@@ -3070,13 +3316,13 @@
       <c r="E36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>113</v>
+      <c r="F36" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36" s="6">
+        <v>173</v>
+      </c>
+      <c r="H36" s="5">
         <v>45839</v>
       </c>
       <c r="I36" s="2">
@@ -3085,28 +3331,31 @@
       <c r="J36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>44866</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="5">
         <v>35936</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>56401</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O36" s="6">
+        <v>184</v>
+      </c>
+      <c r="O36" s="5">
         <v>47265</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2">
         <v>55569</v>
@@ -3117,14 +3366,14 @@
       <c r="E37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>113</v>
+      <c r="F37" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H37" s="6">
-        <v>44927</v>
+        <v>173</v>
+      </c>
+      <c r="H37" s="5">
+        <v>43952</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -3132,29 +3381,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>40163</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>33555</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>54027</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O37" s="6">
+        <v>186</v>
+      </c>
+      <c r="O37" s="5">
         <v>47114</v>
       </c>
-      <c r="S37" s="3"/>
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2">
         <v>74024</v>
@@ -3165,13 +3416,13 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>113</v>
+      <c r="F38" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H38" s="6">
+        <v>173</v>
+      </c>
+      <c r="H38" s="5">
         <v>45474</v>
       </c>
       <c r="I38" s="2">
@@ -3180,29 +3431,31 @@
       <c r="J38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <v>44594</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>36491</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>56949</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O38" s="6">
+        <v>188</v>
+      </c>
+      <c r="O38" s="5">
         <v>46574</v>
       </c>
-      <c r="S38" s="3"/>
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2">
         <v>75329</v>
@@ -3213,13 +3466,13 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>113</v>
+      <c r="F39" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H39" s="6">
+        <v>173</v>
+      </c>
+      <c r="H39" s="5">
         <v>45580</v>
       </c>
       <c r="I39" s="2">
@@ -3228,29 +3481,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
-        <v>44927</v>
-      </c>
-      <c r="L39" s="6">
+      <c r="K39" s="5">
+        <v>44958</v>
+      </c>
+      <c r="L39" s="5">
         <v>37169</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>57650</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="O39" s="6">
+        <v>190</v>
+      </c>
+      <c r="O39" s="5">
         <v>47097</v>
       </c>
-      <c r="S39" s="3"/>
+      <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2">
         <v>74832</v>
@@ -3261,13 +3516,13 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>118</v>
+      <c r="F40" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H40" s="6">
+        <v>173</v>
+      </c>
+      <c r="H40" s="5">
         <v>45366</v>
       </c>
       <c r="I40" s="2">
@@ -3276,29 +3531,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>44866</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>37272</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>57742</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O40" s="6">
+        <v>193</v>
+      </c>
+      <c r="O40" s="5">
         <v>46937</v>
       </c>
-      <c r="S40" s="3"/>
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="C41" s="2">
         <v>49924</v>
@@ -3309,13 +3566,13 @@
       <c r="E41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>118</v>
+      <c r="F41" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41" s="6">
+        <v>173</v>
+      </c>
+      <c r="H41" s="5">
         <v>45383</v>
       </c>
       <c r="I41" s="2">
@@ -3324,29 +3581,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>39387</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>31762</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>52232</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O41" s="6">
+        <v>195</v>
+      </c>
+      <c r="O41" s="5">
         <v>47110</v>
       </c>
-      <c r="S41" s="3"/>
+      <c r="P41" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2">
         <v>46235</v>
@@ -3357,13 +3616,13 @@
       <c r="E42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>121</v>
+      <c r="F42" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H42" s="6">
+        <v>198</v>
+      </c>
+      <c r="H42" s="5">
         <v>45915</v>
       </c>
       <c r="I42" s="2">
@@ -3372,28 +3631,31 @@
       <c r="J42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <v>35490</v>
       </c>
-      <c r="L42" s="6">
-        <v>26885</v>
-      </c>
-      <c r="M42" s="6">
+      <c r="L42" s="5">
+        <v>26879</v>
+      </c>
+      <c r="M42" s="5">
         <v>47362</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O42" s="6">
+        <v>199</v>
+      </c>
+      <c r="O42" s="5">
         <v>47110</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="C43" s="2">
         <v>53210</v>
@@ -3404,13 +3666,13 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>124</v>
+      <c r="F43" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H43" s="6">
+        <v>198</v>
+      </c>
+      <c r="H43" s="5">
         <v>45703</v>
       </c>
       <c r="I43" s="2">
@@ -3419,23 +3681,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <v>39815</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="5">
         <v>32225</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>52688</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="N43" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="O43" s="5">
+        <v>47377</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="44" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2">
         <v>50208</v>
@@ -3446,13 +3716,13 @@
       <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>126</v>
+      <c r="F44" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H44" s="6">
+        <v>198</v>
+      </c>
+      <c r="H44" s="5">
         <v>45308</v>
       </c>
       <c r="I44" s="2">
@@ -3461,29 +3731,22 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>39387</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>32303</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>52779</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O44" s="6">
-        <v>45696</v>
-      </c>
-      <c r="S44" s="3"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>127</v>
+        <v>205</v>
       </c>
       <c r="C45" s="2">
         <v>75334</v>
@@ -3494,13 +3757,13 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>128</v>
+      <c r="F45" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H45" s="6">
+        <v>198</v>
+      </c>
+      <c r="H45" s="5">
         <v>45823</v>
       </c>
       <c r="I45" s="2">
@@ -3509,29 +3772,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>44958</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="5">
         <v>37089</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="5">
         <v>57558</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O45" s="6">
+        <v>207</v>
+      </c>
+      <c r="O45" s="5">
         <v>47265</v>
       </c>
-      <c r="S45" s="3"/>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2">
         <v>71381</v>
@@ -3542,14 +3807,14 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>128</v>
+      <c r="F46" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H46" s="6">
-        <v>44927</v>
+        <v>198</v>
+      </c>
+      <c r="H46" s="5">
+        <v>43556</v>
       </c>
       <c r="I46" s="2">
         <v>5</v>
@@ -3557,23 +3822,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>43075</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>35268</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>55732</v>
       </c>
-      <c r="S46" s="3"/>
+      <c r="N46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="O46" s="5">
+        <v>46407</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C47" s="2">
         <v>74556</v>
@@ -3584,13 +3857,13 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>131</v>
+      <c r="F47" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H47" s="6">
+        <v>198</v>
+      </c>
+      <c r="H47" s="5">
         <v>45383</v>
       </c>
       <c r="I47" s="2">
@@ -3599,29 +3872,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>44866</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>37736</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>58196</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="O47" s="6">
+        <v>212</v>
+      </c>
+      <c r="O47" s="5">
         <v>46916</v>
       </c>
-      <c r="S47" s="3"/>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="C48" s="2">
         <v>69937</v>
@@ -3632,14 +3907,14 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>131</v>
+      <c r="F48" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H48" s="6">
-        <v>44927</v>
+        <v>198</v>
+      </c>
+      <c r="H48" s="5">
+        <v>44531</v>
       </c>
       <c r="I48" s="2">
         <v>5</v>
@@ -3647,23 +3922,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>42597</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>34964</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>55427</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="N48" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O48" s="5">
+        <v>46120</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="C49" s="2">
         <v>53190</v>
@@ -3674,13 +3957,13 @@
       <c r="E49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>131</v>
+      <c r="F49" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H49" s="6">
+        <v>198</v>
+      </c>
+      <c r="H49" s="5">
         <v>45597</v>
       </c>
       <c r="I49" s="2">
@@ -3689,30 +3972,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>39815</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="5">
         <v>31631</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>52110</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="O49" s="6">
+        <v>216</v>
+      </c>
+      <c r="O49" s="5">
         <v>46953</v>
       </c>
-      <c r="P49" s="3"/>
-      <c r="S49" s="3"/>
+      <c r="P49" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="C50" s="2">
         <v>46295</v>
@@ -3723,13 +4007,13 @@
       <c r="E50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>135</v>
+      <c r="F50" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H50" s="6">
+        <v>219</v>
+      </c>
+      <c r="H50" s="5">
         <v>45915</v>
       </c>
       <c r="I50" s="2">
@@ -3738,36 +4022,40 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>35490</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>27978</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>48458</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O50" s="6">
+        <v>220</v>
+      </c>
+      <c r="O50" s="5">
         <v>47110</v>
       </c>
-      <c r="P50" s="3"/>
+      <c r="P50" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q50" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="R50" s="6">
+        <v>221</v>
+      </c>
+      <c r="R50" s="5">
         <v>47265</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="S50" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="51" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2">
         <v>49060</v>
@@ -3778,13 +4066,13 @@
       <c r="E51" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>138</v>
+      <c r="F51" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H51" s="6">
+        <v>219</v>
+      </c>
+      <c r="H51" s="5">
         <v>45823</v>
       </c>
       <c r="I51" s="2">
@@ -3793,24 +4081,31 @@
       <c r="J51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L51" s="6">
+      <c r="K51" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L51" s="5">
         <v>29704</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>50161</v>
       </c>
-      <c r="P51" s="3"/>
-      <c r="S51" s="3"/>
+      <c r="N51" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="O51" s="5">
+        <v>47114</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="52" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2">
         <v>50445</v>
@@ -3821,13 +4116,13 @@
       <c r="E52" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>140</v>
+      <c r="F52" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H52" s="6">
+        <v>219</v>
+      </c>
+      <c r="H52" s="5">
         <v>45672</v>
       </c>
       <c r="I52" s="2">
@@ -3836,30 +4131,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L52" s="6">
-        <v>32847</v>
-      </c>
-      <c r="M52" s="6">
-        <v>53328</v>
+      <c r="K52" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L52" s="5">
+        <v>32640</v>
+      </c>
+      <c r="M52" s="5">
+        <v>53114</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O52" s="6">
+        <v>227</v>
+      </c>
+      <c r="O52" s="5">
         <v>46837</v>
       </c>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
+      <c r="P52" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>141</v>
+        <v>228</v>
       </c>
       <c r="C53" s="2">
         <v>71385</v>
@@ -3870,14 +4166,14 @@
       <c r="E53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>142</v>
+      <c r="F53" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H53" s="6">
-        <v>44927</v>
+        <v>219</v>
+      </c>
+      <c r="H53" s="5">
+        <v>44531</v>
       </c>
       <c r="I53" s="2">
         <v>5</v>
@@ -3885,30 +4181,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <v>43075</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="5">
         <v>34361</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>54820</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O53" s="6">
+        <v>230</v>
+      </c>
+      <c r="O53" s="5">
         <v>46246</v>
       </c>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="P53" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="C54" s="2">
         <v>69941</v>
@@ -3919,14 +4216,14 @@
       <c r="E54" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>142</v>
+      <c r="F54" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H54" s="6">
-        <v>44927</v>
+        <v>219</v>
+      </c>
+      <c r="H54" s="5">
+        <v>43952</v>
       </c>
       <c r="I54" s="2">
         <v>5</v>
@@ -3934,30 +4231,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="5">
         <v>42597</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>33769</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>54240</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="O54" s="6">
+        <v>232</v>
+      </c>
+      <c r="O54" s="5">
         <v>46476</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="P54" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="C55" s="2">
         <v>74562</v>
@@ -3968,13 +4266,13 @@
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>142</v>
+      <c r="F55" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H55" s="6">
+        <v>219</v>
+      </c>
+      <c r="H55" s="5">
         <v>45839</v>
       </c>
       <c r="I55" s="2">
@@ -3983,30 +4281,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="5">
         <v>44866</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="5">
         <v>36970</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>57436</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O55" s="6">
+        <v>234</v>
+      </c>
+      <c r="O55" s="5">
         <v>47005</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="C56" s="2">
         <v>49075</v>
@@ -4017,14 +4316,14 @@
       <c r="E56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>146</v>
+      <c r="F56" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H56" s="6">
-        <v>44927</v>
+        <v>219</v>
+      </c>
+      <c r="H56" s="5">
+        <v>43952</v>
       </c>
       <c r="I56" s="2">
         <v>5</v>
@@ -4032,30 +4331,31 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="5">
         <v>38899</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="5">
         <v>29925</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="5">
         <v>50406</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O56" s="6">
+        <v>237</v>
+      </c>
+      <c r="O56" s="5">
         <v>47110</v>
       </c>
-      <c r="P56" s="3"/>
-      <c r="S56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2">
         <v>71392</v>
@@ -4066,13 +4366,13 @@
       <c r="E57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>146</v>
+      <c r="F57" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H57" s="6">
+        <v>219</v>
+      </c>
+      <c r="H57" s="5">
         <v>45823</v>
       </c>
       <c r="I57" s="2">
@@ -4081,30 +4381,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="5">
         <v>43075</v>
       </c>
-      <c r="L57" s="6">
+      <c r="L57" s="5">
         <v>34593</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>55062</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="O57" s="6">
+        <v>239</v>
+      </c>
+      <c r="O57" s="5">
         <v>46407</v>
       </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="P57" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="C58" s="2">
         <v>75335</v>
@@ -4115,13 +4416,13 @@
       <c r="E58" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>146</v>
+      <c r="F58" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H58" s="6">
+        <v>219</v>
+      </c>
+      <c r="H58" s="5">
         <v>45823</v>
       </c>
       <c r="I58" s="2">
@@ -4130,30 +4431,31 @@
       <c r="J58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>44958</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>38052</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>58532</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O58" s="6">
+        <v>241</v>
+      </c>
+      <c r="O58" s="5">
         <v>47285</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="P58" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2">
         <v>50080</v>
@@ -4164,14 +4466,14 @@
       <c r="E59" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>150</v>
+      <c r="F59" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H59" s="6">
-        <v>45996</v>
+        <v>244</v>
+      </c>
+      <c r="H59" s="5">
+        <v>45915</v>
       </c>
       <c r="I59" s="2">
         <v>8</v>
@@ -4179,30 +4481,31 @@
       <c r="J59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <v>39387</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>32083</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>52566</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O59" s="6">
+        <v>245</v>
+      </c>
+      <c r="O59" s="5">
         <v>47265</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="P59" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="60" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2">
         <v>46300</v>
@@ -4213,13 +4516,13 @@
       <c r="E60" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>153</v>
+      <c r="F60" s="7" t="s">
+        <v>247</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H60" s="6">
+        <v>244</v>
+      </c>
+      <c r="H60" s="5">
         <v>45366</v>
       </c>
       <c r="I60" s="2">
@@ -4228,24 +4531,31 @@
       <c r="J60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <v>35490</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>28025</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>48488</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="N60" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O60" s="5">
+        <v>47110</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="61" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="C61" s="2">
         <v>53185</v>
@@ -4256,13 +4566,13 @@
       <c r="E61" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>155</v>
+      <c r="F61" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H61" s="6">
+        <v>244</v>
+      </c>
+      <c r="H61" s="5">
         <v>45597</v>
       </c>
       <c r="I61" s="2">
@@ -4271,30 +4581,31 @@
       <c r="J61" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>39815</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="5">
         <v>31535</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="5">
         <v>52018</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O61" s="6">
+        <v>251</v>
+      </c>
+      <c r="O61" s="5">
         <v>47370</v>
       </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C62" s="2">
         <v>74694</v>
@@ -4305,13 +4616,13 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>157</v>
+      <c r="F62" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H62" s="6">
+        <v>244</v>
+      </c>
+      <c r="H62" s="5">
         <v>45839</v>
       </c>
       <c r="I62" s="2">
@@ -4320,30 +4631,31 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <v>44866</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>37593</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>58076</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O62" s="6">
+        <v>254</v>
+      </c>
+      <c r="O62" s="5">
         <v>47005</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2">
         <v>77109</v>
@@ -4354,13 +4666,13 @@
       <c r="E63" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>157</v>
+      <c r="F63" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H63" s="6">
+        <v>244</v>
+      </c>
+      <c r="H63" s="5">
         <v>45853</v>
       </c>
       <c r="I63" s="2">
@@ -4369,30 +4681,31 @@
       <c r="J63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="5">
         <v>45566</v>
       </c>
-      <c r="L63" s="6">
+      <c r="L63" s="5">
         <v>36333</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>56796</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="O63" s="6">
+        <v>256</v>
+      </c>
+      <c r="O63" s="5">
         <v>47418</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>159</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2">
         <v>69462</v>
@@ -4403,14 +4716,14 @@
       <c r="E64" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>157</v>
+      <c r="F64" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H64" s="6">
-        <v>44927</v>
+        <v>244</v>
+      </c>
+      <c r="H64" s="5">
+        <v>44162</v>
       </c>
       <c r="I64" s="2">
         <v>5</v>
@@ -4418,30 +4731,31 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="5">
         <v>42562</v>
       </c>
-      <c r="L64" s="6">
+      <c r="L64" s="5">
         <v>34522</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="5">
         <v>55001</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O64" s="6">
+        <v>258</v>
+      </c>
+      <c r="O64" s="5">
         <v>46120</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="P64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="C65" s="2">
         <v>69448</v>
@@ -4452,13 +4766,13 @@
       <c r="E65" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>161</v>
+      <c r="F65" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H65" s="6">
+        <v>244</v>
+      </c>
+      <c r="H65" s="5">
         <v>45823</v>
       </c>
       <c r="I65" s="2">
@@ -4467,41 +4781,48 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>42562</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <v>34086</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>54544</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="N65" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="O65" s="5">
+        <v>46120</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="C66" s="2">
         <v>69446</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>161</v>
+      <c r="F66" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H66" s="8">
+        <v>244</v>
+      </c>
+      <c r="H66" s="5">
         <v>45597</v>
       </c>
       <c r="I66" s="2">
@@ -4510,48 +4831,49 @@
       <c r="J66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>42562</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <v>33398</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <v>53874</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O66" s="6">
+        <v>263</v>
+      </c>
+      <c r="O66" s="5">
         <v>46120</v>
       </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="P66" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="C67" s="2">
         <v>69940</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>161</v>
+      <c r="F67" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H67" s="8">
-        <v>44927</v>
+        <v>244</v>
+      </c>
+      <c r="H67" s="5">
+        <v>43952</v>
       </c>
       <c r="I67" s="2">
         <v>5</v>
@@ -4559,47 +4881,48 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>42597</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>34202</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>54667</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O67" s="6">
+        <v>265</v>
+      </c>
+      <c r="O67" s="5">
         <v>46120</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="P67" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="C68" s="2">
         <v>74821</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>161</v>
+      <c r="F68" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H68" s="6">
+        <v>244</v>
+      </c>
+      <c r="H68" s="5">
         <v>45505</v>
       </c>
       <c r="I68" s="2">
@@ -4608,47 +4931,48 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <v>44866</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>37543</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="5">
         <v>58015</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="O68" s="6">
+        <v>267</v>
+      </c>
+      <c r="O68" s="5">
         <v>47008</v>
       </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="C69" s="2">
         <v>48999</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>166</v>
+      <c r="F69" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H69" s="8">
+        <v>270</v>
+      </c>
+      <c r="H69" s="5">
         <v>45915</v>
       </c>
       <c r="I69" s="2">
@@ -4657,53 +4981,48 @@
       <c r="J69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <v>38899</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>29188</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>49644</v>
       </c>
-      <c r="N69" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O69" s="6">
-        <v>45747</v>
-      </c>
-      <c r="P69" s="3"/>
       <c r="Q69" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="R69" s="6">
+        <v>271</v>
+      </c>
+      <c r="R69" s="5">
         <v>47232</v>
       </c>
-      <c r="S69" s="3"/>
+      <c r="S69" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="70" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="C70" s="2">
         <v>46248</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>169</v>
+      <c r="F70" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H70" s="8">
+        <v>270</v>
+      </c>
+      <c r="H70" s="5">
         <v>45308</v>
       </c>
       <c r="I70" s="2">
@@ -4712,42 +5031,49 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <v>35490</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="5">
         <v>27222</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="5">
         <v>47696</v>
       </c>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
+      <c r="N70" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O70" s="5">
+        <v>47110</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="71" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="C71" s="2">
         <v>46280</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>171</v>
+      <c r="F71" s="7" t="s">
+        <v>276</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H71" s="6">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H71" s="5">
+        <v>43952</v>
       </c>
       <c r="I71" s="2">
         <v>7</v>
@@ -4755,48 +5081,49 @@
       <c r="J71" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L71" s="6">
+      <c r="K71" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L71" s="5">
         <v>27774</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>48245</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O71" s="6">
+        <v>277</v>
+      </c>
+      <c r="O71" s="5">
         <v>47110</v>
       </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
+      <c r="P71" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="C72" s="2">
         <v>53309</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>173</v>
+      <c r="F72" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H72" s="6">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H72" s="5">
+        <v>43952</v>
       </c>
       <c r="I72" s="2">
         <v>5</v>
@@ -4804,42 +5131,49 @@
       <c r="J72" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L72" s="6">
+      <c r="K72" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L72" s="5">
         <v>33013</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>53479</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
+      <c r="N72" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="O72" s="5">
+        <v>47110</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="C73" s="2">
         <v>55606</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>173</v>
+      <c r="F73" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H73" s="8">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H73" s="5">
+        <v>44531</v>
       </c>
       <c r="I73" s="2">
         <v>5</v>
@@ -4847,47 +5181,48 @@
       <c r="J73" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>40163</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>32830</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="5">
         <v>53297</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O73" s="6">
+        <v>282</v>
+      </c>
+      <c r="O73" s="5">
         <v>47110</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="P73" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2">
         <v>75332</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>173</v>
+      <c r="F74" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H74" s="8">
+        <v>270</v>
+      </c>
+      <c r="H74" s="5">
         <v>45853</v>
       </c>
       <c r="I74" s="2">
@@ -4896,42 +5231,49 @@
       <c r="J74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K74" s="6">
-        <v>44927</v>
-      </c>
-      <c r="L74" s="6">
+      <c r="K74" s="5">
+        <v>44958</v>
+      </c>
+      <c r="L74" s="5">
         <v>35877</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="5">
         <v>56340</v>
       </c>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
+      <c r="N74" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="O74" s="5">
+        <v>47110</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="C75" s="2">
         <v>53192</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>177</v>
+      <c r="F75" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H75" s="8">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H75" s="5">
+        <v>44531</v>
       </c>
       <c r="I75" s="2">
         <v>5</v>
@@ -4939,48 +5281,49 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L75" s="6">
+      <c r="K75" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L75" s="5">
         <v>31727</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>52201</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O75" s="6">
+        <v>287</v>
+      </c>
+      <c r="O75" s="5">
         <v>47110</v>
       </c>
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
+      <c r="P75" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>178</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2">
         <v>53214</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>177</v>
+      <c r="F76" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H76" s="8">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H76" s="5">
+        <v>43952</v>
       </c>
       <c r="I76" s="2">
         <v>5</v>
@@ -4988,48 +5331,49 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L76" s="6">
+      <c r="K76" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L76" s="5">
         <v>32348</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="5">
         <v>52810</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O76" s="6">
+        <v>289</v>
+      </c>
+      <c r="O76" s="5">
         <v>47110</v>
       </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="P76" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="C77" s="2">
         <v>69942</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>177</v>
+      <c r="F77" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H77" s="8">
-        <v>44927</v>
+        <v>270</v>
+      </c>
+      <c r="H77" s="5">
+        <v>43952</v>
       </c>
       <c r="I77" s="2">
         <v>5</v>
@@ -5037,47 +5381,48 @@
       <c r="J77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="5">
         <v>42597</v>
       </c>
-      <c r="L77" s="6">
-        <v>35075</v>
-      </c>
-      <c r="M77" s="6">
-        <v>55550</v>
+      <c r="L77" s="5">
+        <v>35370</v>
+      </c>
+      <c r="M77" s="5">
+        <v>55854</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O77" s="6">
+        <v>291</v>
+      </c>
+      <c r="O77" s="5">
         <v>47110</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
+      <c r="P77" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="C78" s="2">
         <v>44390</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>181</v>
+      <c r="F78" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H78" s="8">
+        <v>294</v>
+      </c>
+      <c r="H78" s="5">
         <v>45458</v>
       </c>
       <c r="I78" s="2">
@@ -5086,41 +5431,57 @@
       <c r="J78" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="5">
         <v>35217</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="5">
         <v>26079</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="5">
         <v>46539</v>
       </c>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
+      <c r="N78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="O78" s="5">
+        <v>47203</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="R78" s="5">
+        <v>47097</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="79" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="C79" s="2">
         <v>46222</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>184</v>
+      <c r="F79" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H79" s="8">
+        <v>294</v>
+      </c>
+      <c r="H79" s="5">
         <v>45308</v>
       </c>
       <c r="I79" s="2">
@@ -5129,47 +5490,48 @@
       <c r="J79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="5">
         <v>35490</v>
       </c>
-      <c r="L79" s="6">
+      <c r="L79" s="5">
         <v>26488</v>
       </c>
-      <c r="M79" s="6">
+      <c r="M79" s="5">
         <v>46966</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="O79" s="6">
+        <v>299</v>
+      </c>
+      <c r="O79" s="5">
         <v>46851</v>
       </c>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
+      <c r="P79" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="80" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="C80" s="2">
         <v>50086</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>186</v>
+      <c r="F80" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H80" s="8">
+        <v>294</v>
+      </c>
+      <c r="H80" s="5">
         <v>45566</v>
       </c>
       <c r="I80" s="2">
@@ -5178,48 +5540,49 @@
       <c r="J80" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="5">
         <v>39387</v>
       </c>
-      <c r="L80" s="6">
+      <c r="L80" s="5">
         <v>32093</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="5">
         <v>52566</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="O80" s="6">
+        <v>302</v>
+      </c>
+      <c r="O80" s="5">
         <v>46937</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P80" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="C81" s="2">
         <v>50235</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>188</v>
+      <c r="F81" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H81" s="6">
-        <v>44927</v>
+        <v>294</v>
+      </c>
+      <c r="H81" s="5">
+        <v>44531</v>
       </c>
       <c r="I81" s="2">
         <v>5</v>
@@ -5227,47 +5590,48 @@
       <c r="J81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L81" s="6">
-        <v>32332</v>
-      </c>
-      <c r="M81" s="6">
-        <v>52810</v>
+      <c r="K81" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L81" s="5">
+        <v>32362</v>
+      </c>
+      <c r="M81" s="5">
+        <v>52841</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="O81" s="6">
+        <v>305</v>
+      </c>
+      <c r="O81" s="5">
         <v>47110</v>
       </c>
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P81" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>189</v>
+        <v>306</v>
       </c>
       <c r="C82" s="2">
         <v>71387</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>188</v>
+      <c r="F82" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H82" s="6">
+        <v>294</v>
+      </c>
+      <c r="H82" s="5">
         <v>45853</v>
       </c>
       <c r="I82" s="2">
@@ -5276,47 +5640,48 @@
       <c r="J82" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K82" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L82" s="6">
+      <c r="K82" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L82" s="5">
         <v>35078</v>
       </c>
-      <c r="M82" s="6">
+      <c r="M82" s="5">
         <v>55550</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="O82" s="6">
+        <v>307</v>
+      </c>
+      <c r="O82" s="5">
         <v>46246</v>
       </c>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P82" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>190</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2">
         <v>77107</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>188</v>
+      <c r="F83" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H83" s="6">
+        <v>294</v>
+      </c>
+      <c r="H83" s="5">
         <v>45853</v>
       </c>
       <c r="I83" s="2">
@@ -5325,41 +5690,39 @@
       <c r="J83" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="5">
         <v>45566</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="5">
         <v>36436</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="5">
         <v>56919</v>
       </c>
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>191</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2">
         <v>74736</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>192</v>
+      <c r="F84" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H84" s="8">
+        <v>294</v>
+      </c>
+      <c r="H84" s="5">
         <v>45853</v>
       </c>
       <c r="I84" s="2">
@@ -5368,48 +5731,49 @@
       <c r="J84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>44866</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>37601</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="5">
         <v>58076</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O84" s="6">
+        <v>311</v>
+      </c>
+      <c r="O84" s="5">
         <v>47054</v>
       </c>
-      <c r="P84" s="3"/>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P84" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="C85" s="2">
         <v>71383</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>192</v>
+      <c r="F85" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H85" s="8">
-        <v>44927</v>
+        <v>294</v>
+      </c>
+      <c r="H85" s="5">
+        <v>43952</v>
       </c>
       <c r="I85" s="2">
         <v>5</v>
@@ -5417,41 +5781,48 @@
       <c r="J85" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K85" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L85" s="6">
+      <c r="K85" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L85" s="5">
         <v>35051</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="5">
         <v>55519</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N85" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="O85" s="5">
+        <v>46259</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="C86" s="2">
         <v>49088</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>195</v>
+      <c r="F86" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H86" s="8">
+        <v>316</v>
+      </c>
+      <c r="H86" s="5">
         <v>45823</v>
       </c>
       <c r="I86" s="2">
@@ -5460,47 +5831,48 @@
       <c r="J86" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K86" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L86" s="6">
-        <v>30439</v>
-      </c>
-      <c r="M86" s="6">
-        <v>50922</v>
+      <c r="K86" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L86" s="5">
+        <v>30380</v>
+      </c>
+      <c r="M86" s="5">
+        <v>50861</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="O86" s="6">
+        <v>317</v>
+      </c>
+      <c r="O86" s="5">
         <v>47110</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P86" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>197</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2">
         <v>49014</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>198</v>
+      <c r="F87" s="7" t="s">
+        <v>319</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H87" s="6">
+        <v>316</v>
+      </c>
+      <c r="H87" s="5">
         <v>45597</v>
       </c>
       <c r="I87" s="2">
@@ -5509,47 +5881,48 @@
       <c r="J87" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="5">
         <v>38899</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="5">
         <v>29278</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="5">
         <v>49735</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="O87" s="6">
+        <v>320</v>
+      </c>
+      <c r="O87" s="5">
         <v>46837</v>
       </c>
-      <c r="P87" s="3"/>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P87" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>199</v>
+        <v>321</v>
       </c>
       <c r="C88" s="2">
         <v>50348</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>200</v>
+      <c r="F88" s="7" t="s">
+        <v>322</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H88" s="8">
+        <v>316</v>
+      </c>
+      <c r="H88" s="5">
         <v>45703</v>
       </c>
       <c r="I88" s="2">
@@ -5558,54 +5931,49 @@
       <c r="J88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="5">
         <v>39387</v>
       </c>
-      <c r="L88" s="6">
+      <c r="L88" s="5">
         <v>32519</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="5">
         <v>52994</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="O88" s="6">
+        <v>323</v>
+      </c>
+      <c r="O88" s="5">
         <v>46727</v>
       </c>
-      <c r="P88" s="3"/>
-      <c r="Q88" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="R88" s="6">
-        <v>46727</v>
-      </c>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P88" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="C89" s="2">
         <v>51196</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>202</v>
+      <c r="F89" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H89" s="6">
-        <v>44927</v>
+        <v>316</v>
+      </c>
+      <c r="H89" s="5">
+        <v>43952</v>
       </c>
       <c r="I89" s="2">
         <v>5</v>
@@ -5613,47 +5981,48 @@
       <c r="J89" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="5">
         <v>39600</v>
       </c>
-      <c r="L89" s="6">
-        <v>26187</v>
-      </c>
-      <c r="M89" s="6">
-        <v>46661</v>
+      <c r="L89" s="5">
+        <v>26246</v>
+      </c>
+      <c r="M89" s="5">
+        <v>46722</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O89" s="6">
+        <v>326</v>
+      </c>
+      <c r="O89" s="5">
         <v>47110</v>
       </c>
-      <c r="P89" s="3"/>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P89" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="C90" s="2">
         <v>76922</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>204</v>
+      <c r="F90" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H90" s="6">
+        <v>316</v>
+      </c>
+      <c r="H90" s="5">
         <v>45823</v>
       </c>
       <c r="I90" s="2">
@@ -5662,45 +6031,48 @@
       <c r="J90" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="5">
         <v>45289</v>
       </c>
-      <c r="L90" s="6">
+      <c r="L90" s="5">
         <v>36005</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="5">
         <v>56462</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O90" s="6">
+        <v>329</v>
+      </c>
+      <c r="O90" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P90" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="C91" s="2">
         <v>74578</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>202</v>
+      <c r="F91" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H91" s="6">
+        <v>316</v>
+      </c>
+      <c r="H91" s="5">
         <v>45839</v>
       </c>
       <c r="I91" s="2">
@@ -5709,45 +6081,48 @@
       <c r="J91" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="5">
         <v>44866</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="5">
         <v>37658</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="5">
         <v>58135</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="O91" s="6">
+        <v>331</v>
+      </c>
+      <c r="O91" s="5">
         <v>47005</v>
       </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P91" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>206</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2">
         <v>48244</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>204</v>
+      <c r="F92" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H92" s="6">
+        <v>316</v>
+      </c>
+      <c r="H92" s="5">
         <v>45853</v>
       </c>
       <c r="I92" s="2">
@@ -5756,46 +6131,49 @@
       <c r="J92" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K92" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L92" s="6">
-        <v>27951</v>
-      </c>
-      <c r="M92" s="6">
-        <v>48427</v>
+      <c r="K92" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L92" s="5">
+        <v>28040</v>
+      </c>
+      <c r="M92" s="5">
+        <v>48519</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O92" s="6">
+        <v>333</v>
+      </c>
+      <c r="O92" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P92" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>207</v>
+        <v>334</v>
       </c>
       <c r="C93" s="2">
         <v>51244</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>204</v>
+      <c r="F93" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H93" s="6">
-        <v>44927</v>
+        <v>316</v>
+      </c>
+      <c r="H93" s="5">
+        <v>43952</v>
       </c>
       <c r="I93" s="2">
         <v>5</v>
@@ -5803,39 +6181,48 @@
       <c r="J93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K93" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L93" s="6">
+      <c r="K93" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L93" s="5">
         <v>27782</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="5">
         <v>48245</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N93" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="O93" s="5">
+        <v>46060</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>208</v>
+        <v>336</v>
       </c>
       <c r="C94" s="2">
         <v>43915</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>209</v>
+      <c r="F94" s="7" t="s">
+        <v>337</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H94" s="6">
+        <v>338</v>
+      </c>
+      <c r="H94" s="5">
         <v>45870</v>
       </c>
       <c r="I94" s="2">
@@ -5844,40 +6231,49 @@
       <c r="J94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="6">
+      <c r="K94" s="5">
         <v>35217</v>
       </c>
-      <c r="L94" s="6">
+      <c r="L94" s="5">
         <v>28301</v>
       </c>
-      <c r="M94" s="6">
+      <c r="M94" s="5">
         <v>48761</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N94" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="O94" s="5">
+        <v>47005</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="C95" s="2">
         <v>46217</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>212</v>
+      <c r="F95" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H95" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H95" s="5">
+        <v>44057</v>
       </c>
       <c r="I95" s="2">
         <v>8</v>
@@ -5885,40 +6281,49 @@
       <c r="J95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K95" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L95" s="6">
-        <v>26329</v>
-      </c>
-      <c r="M95" s="6">
+      <c r="K95" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L95" s="5">
+        <v>27425</v>
+      </c>
+      <c r="M95" s="5">
         <v>46784</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N95" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="O95" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>214</v>
+        <v>344</v>
       </c>
       <c r="C96" s="2">
         <v>46272</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>215</v>
+      <c r="F96" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H96" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H96" s="5">
+        <v>44593</v>
       </c>
       <c r="I96" s="2">
         <v>8</v>
@@ -5926,46 +6331,49 @@
       <c r="J96" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K96" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L96" s="6">
+      <c r="K96" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L96" s="5">
         <v>27614</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="5">
         <v>48092</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="O96" s="6">
+        <v>346</v>
+      </c>
+      <c r="O96" s="5">
         <v>46837</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P96" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>216</v>
+        <v>347</v>
       </c>
       <c r="C97" s="2">
         <v>53188</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>217</v>
+      <c r="F97" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H97" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H97" s="5">
+        <v>43952</v>
       </c>
       <c r="I97" s="2">
         <v>5</v>
@@ -5973,46 +6381,49 @@
       <c r="J97" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K97" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L97" s="6">
-        <v>31570</v>
-      </c>
-      <c r="M97" s="6">
-        <v>52048</v>
+      <c r="K97" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L97" s="5">
+        <v>31599</v>
+      </c>
+      <c r="M97" s="5">
+        <v>52079</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O97" s="6">
+        <v>349</v>
+      </c>
+      <c r="O97" s="5">
         <v>46861</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>218</v>
+        <v>350</v>
       </c>
       <c r="C98" s="2">
         <v>60162</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>217</v>
+      <c r="F98" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H98" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H98" s="5">
+        <v>44162</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
@@ -6020,46 +6431,49 @@
       <c r="J98" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98" s="5">
         <v>40575</v>
       </c>
-      <c r="L98" s="6">
+      <c r="L98" s="5">
         <v>32012</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="5">
         <v>52475</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O98" s="6">
+        <v>351</v>
+      </c>
+      <c r="O98" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>219</v>
+        <v>352</v>
       </c>
       <c r="C99" s="2">
         <v>51192</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>217</v>
+      <c r="F99" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H99" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H99" s="5">
+        <v>43952</v>
       </c>
       <c r="I99" s="2">
         <v>5</v>
@@ -6067,45 +6481,48 @@
       <c r="J99" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K99" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L99" s="6">
+      <c r="K99" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L99" s="5">
         <v>26189</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="5">
         <v>46661</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O99" s="6">
+        <v>353</v>
+      </c>
+      <c r="O99" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P99" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>220</v>
+        <v>354</v>
       </c>
       <c r="C100" s="2">
         <v>75331</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>217</v>
+      <c r="F100" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H100" s="6">
+        <v>342</v>
+      </c>
+      <c r="H100" s="5">
         <v>45853</v>
       </c>
       <c r="I100" s="2">
@@ -6114,46 +6531,49 @@
       <c r="J100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="5">
         <v>44958</v>
       </c>
-      <c r="L100" s="6">
+      <c r="L100" s="5">
         <v>38041</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="5">
         <v>58501</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O100" s="6">
+        <v>355</v>
+      </c>
+      <c r="O100" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P100" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>221</v>
+        <v>356</v>
       </c>
       <c r="C101" s="2">
         <v>48003</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>222</v>
+      <c r="F101" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H101" s="6">
-        <v>44927</v>
+        <v>342</v>
+      </c>
+      <c r="H101" s="5">
+        <v>43952</v>
       </c>
       <c r="I101" s="2">
         <v>5</v>
@@ -6161,45 +6581,48 @@
       <c r="J101" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L101" s="6">
+      <c r="K101" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L101" s="5">
         <v>26416</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="5">
         <v>46874</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O101" s="6">
+        <v>358</v>
+      </c>
+      <c r="O101" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>223</v>
+        <v>359</v>
       </c>
       <c r="C102" s="2">
         <v>69589</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>222</v>
+      <c r="F102" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H102" s="6">
+        <v>342</v>
+      </c>
+      <c r="H102" s="5">
         <v>45566</v>
       </c>
       <c r="I102" s="2">
@@ -6208,46 +6631,165 @@
       <c r="J102" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K102" s="6">
+      <c r="K102" s="5">
         <v>42562</v>
       </c>
-      <c r="L102" s="6">
+      <c r="L102" s="5">
         <v>33381</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="5">
         <v>53844</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O102" s="6">
+        <v>360</v>
+      </c>
+      <c r="O102" s="5">
         <v>46120</v>
       </c>
-    </row>
+      <c r="P102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T145" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D991</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J991</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I991</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6257,130 +6799,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
